--- a/submissions/med/supplement/Supplemental_Tables.xlsx
+++ b/submissions/med/supplement/Supplemental_Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wanjun/Desktop/GastricBypass/submissions/med/supplement/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wgu/Desktop/GastricBypass/submissions/med/supplement/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F51EA111-D2A7-6F42-9A5C-2870C1D35A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="1" xr2:uid="{AF6A1B50-D1C6-BB40-9E02-3E114CB2C68C}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{AF6A1B50-D1C6-BB40-9E02-3E114CB2C68C}"/>
   </bookViews>
   <sheets>
     <sheet name="Supplemental Table 1" sheetId="1" r:id="rId1"/>
@@ -2123,6 +2123,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2144,59 +2147,56 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2527,10 +2527,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="42" t="s">
         <v>358</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="44" t="s">
         <v>387</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -2539,20 +2539,20 @@
       <c r="D2" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="40" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="40" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="42"/>
-      <c r="B3" s="44"/>
+      <c r="A3" s="43"/>
+      <c r="B3" s="45"/>
       <c r="C3" s="31" t="s">
         <v>476</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>475</v>
       </c>
-      <c r="E3" s="40"/>
+      <c r="E3" s="41"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
@@ -3402,17 +3402,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="39" t="s">
         <v>255</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="63"/>
-      <c r="H1" s="63"/>
-      <c r="I1" s="63"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
     </row>
     <row r="2" spans="1:9" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
@@ -5235,263 +5235,263 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="46" t="s">
         <v>260</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="49" t="s">
         <v>122</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="52" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="57"/>
-      <c r="B4" s="58"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="50"/>
       <c r="C4" s="16" t="s">
         <v>263</v>
       </c>
-      <c r="D4" s="59"/>
+      <c r="D4" s="53"/>
     </row>
     <row r="5" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="57"/>
-      <c r="B5" s="58"/>
+      <c r="A5" s="47"/>
+      <c r="B5" s="50"/>
       <c r="C5" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="D5" s="59"/>
+      <c r="D5" s="53"/>
     </row>
     <row r="6" spans="1:4" ht="80" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="46"/>
-      <c r="B6" s="48"/>
+      <c r="A6" s="48"/>
+      <c r="B6" s="51"/>
       <c r="C6" s="17" t="s">
         <v>265</v>
       </c>
-      <c r="D6" s="50"/>
+      <c r="D6" s="54"/>
     </row>
     <row r="7" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="55" t="s">
         <v>266</v>
       </c>
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="58" t="s">
         <v>267</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="D7" s="55" t="s">
+      <c r="D7" s="61" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="60"/>
-      <c r="B8" s="61"/>
+      <c r="A8" s="56"/>
+      <c r="B8" s="59"/>
       <c r="C8" s="19" t="s">
         <v>270</v>
       </c>
       <c r="D8" s="62"/>
     </row>
     <row r="9" spans="1:4" ht="80" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="52"/>
-      <c r="B9" s="54"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="60"/>
       <c r="C9" s="20" t="s">
         <v>271</v>
       </c>
-      <c r="D9" s="56"/>
+      <c r="D9" s="63"/>
     </row>
     <row r="10" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="45" t="s">
+      <c r="A10" s="46" t="s">
         <v>272</v>
       </c>
-      <c r="B10" s="47" t="s">
+      <c r="B10" s="49" t="s">
         <v>273</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="D10" s="49" t="s">
+      <c r="D10" s="52" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="80" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="46"/>
-      <c r="B11" s="48"/>
+      <c r="A11" s="48"/>
+      <c r="B11" s="51"/>
       <c r="C11" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="D11" s="50"/>
+      <c r="D11" s="54"/>
     </row>
     <row r="12" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="55" t="s">
         <v>277</v>
       </c>
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="58" t="s">
         <v>278</v>
       </c>
       <c r="C12" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="D12" s="55" t="s">
+      <c r="D12" s="61" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="60"/>
-      <c r="B13" s="61"/>
+      <c r="A13" s="56"/>
+      <c r="B13" s="59"/>
       <c r="C13" s="19" t="s">
         <v>281</v>
       </c>
       <c r="D13" s="62"/>
     </row>
     <row r="14" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="60"/>
-      <c r="B14" s="61"/>
+      <c r="A14" s="56"/>
+      <c r="B14" s="59"/>
       <c r="C14" s="19" t="s">
         <v>282</v>
       </c>
       <c r="D14" s="62"/>
     </row>
     <row r="15" spans="1:4" ht="100" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="52"/>
-      <c r="B15" s="54"/>
+      <c r="A15" s="57"/>
+      <c r="B15" s="60"/>
       <c r="C15" s="20" t="s">
         <v>283</v>
       </c>
-      <c r="D15" s="56"/>
+      <c r="D15" s="63"/>
     </row>
     <row r="16" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="45" t="s">
+      <c r="A16" s="46" t="s">
         <v>284</v>
       </c>
-      <c r="B16" s="47" t="s">
+      <c r="B16" s="49" t="s">
         <v>198</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="52" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="57"/>
-      <c r="B17" s="58"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="50"/>
       <c r="C17" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="D17" s="59"/>
+      <c r="D17" s="53"/>
     </row>
     <row r="18" spans="1:4" ht="80" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="46"/>
-      <c r="B18" s="48"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="51"/>
       <c r="C18" s="17" t="s">
         <v>288</v>
       </c>
-      <c r="D18" s="50"/>
+      <c r="D18" s="54"/>
     </row>
     <row r="19" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="51" t="s">
+      <c r="A19" s="55" t="s">
         <v>289</v>
       </c>
-      <c r="B19" s="53" t="s">
+      <c r="B19" s="58" t="s">
         <v>290</v>
       </c>
       <c r="C19" s="18" t="s">
         <v>291</v>
       </c>
-      <c r="D19" s="55" t="s">
+      <c r="D19" s="61" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="60"/>
-      <c r="B20" s="61"/>
+      <c r="A20" s="56"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="21" t="s">
         <v>293</v>
       </c>
       <c r="D20" s="62"/>
     </row>
     <row r="21" spans="1:4" ht="80" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="52"/>
-      <c r="B21" s="54"/>
+      <c r="A21" s="57"/>
+      <c r="B21" s="60"/>
       <c r="C21" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="D21" s="56"/>
+      <c r="D21" s="63"/>
     </row>
     <row r="22" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="45" t="s">
+      <c r="A22" s="46" t="s">
         <v>295</v>
       </c>
-      <c r="B22" s="47" t="s">
+      <c r="B22" s="49" t="s">
         <v>296</v>
       </c>
       <c r="C22" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="D22" s="49" t="s">
+      <c r="D22" s="52" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="80" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="46"/>
-      <c r="B23" s="48"/>
+      <c r="A23" s="48"/>
+      <c r="B23" s="51"/>
       <c r="C23" s="17" t="s">
         <v>299</v>
       </c>
-      <c r="D23" s="50"/>
+      <c r="D23" s="54"/>
     </row>
     <row r="24" spans="1:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="51" t="s">
+      <c r="A24" s="55" t="s">
         <v>300</v>
       </c>
-      <c r="B24" s="53" t="s">
+      <c r="B24" s="58" t="s">
         <v>301</v>
       </c>
       <c r="C24" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="D24" s="55" t="s">
+      <c r="D24" s="61" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="80" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="52"/>
-      <c r="B25" s="54"/>
+      <c r="A25" s="57"/>
+      <c r="B25" s="60"/>
       <c r="C25" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="D25" s="56"/>
+      <c r="D25" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="D12:D15"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="B3:B6"/>
     <mergeCell ref="D3:D6"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="B7:B9"/>
     <mergeCell ref="D7:D9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="D12:D15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="D24:D25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
